--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/11. ООО ЛИКАРД (топливо Лукойл)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/11. ООО ЛИКАРД (топливо Лукойл)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92568660918</v>
+        <v>46157.93099017013</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/11. ООО ЛИКАРД (топливо Лукойл)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/11. ООО ЛИКАРД (топливо Лукойл)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93099017013</v>
+        <v>46157.93173665628</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/11. ООО ЛИКАРД (топливо Лукойл)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/11. ООО ЛИКАРД (топливо Лукойл)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93173665628</v>
+        <v>46157.9340046767</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/11. ООО ЛИКАРД (топливо Лукойл)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/11. ООО ЛИКАРД (топливо Лукойл)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9340046767</v>
+        <v>46157.93718365298</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/11. ООО ЛИКАРД (топливо Лукойл)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/11. ООО ЛИКАРД (топливо Лукойл)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93718365298</v>
+        <v>46158.28216670465</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/11. ООО ЛИКАРД (топливо Лукойл)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/11. ООО ЛИКАРД (топливо Лукойл)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28216670465</v>
+        <v>46158.29682053762</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/11. ООО ЛИКАРД (топливо Лукойл)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/11. ООО ЛИКАРД (топливо Лукойл)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29682053762</v>
+        <v>46158.29815076994</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/11. ООО ЛИКАРД (топливо Лукойл)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/11. ООО ЛИКАРД (топливо Лукойл)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29815076994</v>
+        <v>46158.33387710056</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/11. ООО ЛИКАРД (топливо Лукойл)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/11. ООО ЛИКАРД (топливо Лукойл)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33387710056</v>
+        <v>46158.36857521214</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/11. ООО ЛИКАРД (топливо Лукойл)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/11. ООО ЛИКАРД (топливо Лукойл)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36857521214</v>
+        <v>46158.37288140382</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
